--- a/HOOKS_GUIDE.xlsx
+++ b/HOOKS_GUIDE.xlsx
@@ -1254,12 +1254,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>[resource-scout-integrator], [github-talent-scout], [skill-forge-builder], [agent-optimizer], [git-github-manager]</t>
+          <t>[resource-scout-integrator], [github-talent-scout], [skill-forge-builder], [agent-optimizer], [frontend-design-builder], [git-github-manager]</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>تحليل المستودعات الخارجية واستيراد المهارات وتعميمها عالمياً وتحديث الخطافات ومزامنة مستودع Claude-Antigravity-Workspace.</t>
+          <t>تحليل المستودعات الخارجية واستيراد المهارات وتعميمها وتحديث الخطافات والإكسيل وتطبيق مكتبة الأوامر ومزامنة المنظومة.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
   1. **فحص وتقييم المورد (`resource-scout-integrator` + `github-talent-scout`):** استلام رابط المستودع الخارجي وفحص ملفات README والأكواد وتحديد ما إذا كان يُحدث نقلة نوعية واستبعاد ما لا يتوافق مع البيئة.
   2. **بناء وهيكلة المهارات (`skill-forge-builder`):** استخراج المهارات الفعالة وصياغة ملفات `SKILL.md` وفق المعايير العالمية.
   3. **التعميم العالمي (`global-deployment`):** نشر المهارات في `C:\Users\Kt\.gemini\config\skills/` لتصبح متاحة لكل المشاريع.
-  4. **تحديث الخطافات والإكسيل (`agent-optimizer`):** إضافة المهارات للخطافات ذات الصلة وتشغيل سكربت `convert_hooks_to_sheets.py` لتحديث ملف الإكسيل `HOOKS_GUIDE.xlsx`.
+  4. **تحديث الخطافات والإكسيل وتطبيق مكتبة الأوامر (`agent-optimizer` + `frontend-design-builder`):** إضافة المهارات للخطافات ذات الصلة وتشغيل سكربت `convert_hooks_to_sheets.py` لتحديث ملف الإكسيل `HOOKS_GUIDE.xlsx` وتشغيل `update_html.py` لتحديث تطبيق مكتبة الأوامر التفاعلي (`03_Dynamic_Prompt_Library/index.html`).
   5. **مزامنة المستودع العام سحابياً (`git-github-manager`):** تشغيل `sync_global_ecosystem.py` لمزامنة كامل منظومة الوكلاء والمهارات والدليل مع مستودع `Claude-Antigravity-Workspace` ورفعه إلى GitHub.
 &lt;/div&gt;</t>
         </is>
@@ -2452,12 +2452,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[resource-scout-integrator], [github-talent-scout], [skill-forge-builder], [agent-optimizer], [git-github-manager]</t>
+          <t>[resource-scout-integrator], [github-talent-scout], [skill-forge-builder], [agent-optimizer], [frontend-design-builder], [git-github-manager]</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>تحليل المستودعات الخارجية واستيراد المهارات وتعميمها عالمياً وتحديث الخطافات ومزامنة مستودع Claude-Antigravity-Workspace.</t>
+          <t>تحليل المستودعات الخارجية واستيراد المهارات وتعميمها وتحديث الخطافات والإكسيل وتطبيق مكتبة الأوامر ومزامنة المنظومة.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
   1. **فحص وتقييم المورد (`resource-scout-integrator` + `github-talent-scout`):** استلام رابط المستودع الخارجي وفحص ملفات README والأكواد وتحديد ما إذا كان يُحدث نقلة نوعية واستبعاد ما لا يتوافق مع البيئة.
   2. **بناء وهيكلة المهارات (`skill-forge-builder`):** استخراج المهارات الفعالة وصياغة ملفات `SKILL.md` وفق المعايير العالمية.
   3. **التعميم العالمي (`global-deployment`):** نشر المهارات في `C:\Users\Kt\.gemini\config\skills/` لتصبح متاحة لكل المشاريع.
-  4. **تحديث الخطافات والإكسيل (`agent-optimizer`):** إضافة المهارات للخطافات ذات الصلة وتشغيل سكربت `convert_hooks_to_sheets.py` لتحديث ملف الإكسيل `HOOKS_GUIDE.xlsx`.
+  4. **تحديث الخطافات والإكسيل وتطبيق مكتبة الأوامر (`agent-optimizer` + `frontend-design-builder`):** إضافة المهارات للخطافات ذات الصلة وتشغيل سكربت `convert_hooks_to_sheets.py` لتحديث ملف الإكسيل `HOOKS_GUIDE.xlsx` وتشغيل `update_html.py` لتحديث تطبيق مكتبة الأوامر التفاعلي (`03_Dynamic_Prompt_Library/index.html`).
   5. **مزامنة المستودع العام سحابياً (`git-github-manager`):** تشغيل `sync_global_ecosystem.py` لمزامنة كامل منظومة الوكلاء والمهارات والدليل مع مستودع `Claude-Antigravity-Workspace` ورفعه إلى GitHub.
 &lt;/div&gt;</t>
         </is>

--- a/HOOKS_GUIDE.xlsx
+++ b/HOOKS_GUIDE.xlsx
@@ -533,8 +533,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.6 Flash (Medium)` 
- البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+          <t>الأساسي: `Gemini 2.0 Flash` 
+ البديل: `Claude 3.5 Haiku`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -572,8 +572,8 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
- البديل: `Claude Opus 4.6 (Thinking)`</t>
+          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
+ البديل: `Gemini 2.0 Pro`</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -612,8 +612,8 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
- البديل: `Gemini 3.1 Pro (High)`</t>
+          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
+ البديل: `Gemini 2.0 Pro (Thinking)`</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -652,8 +652,8 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.1 Pro (High)` 
- البديل: `Claude Opus 4.6 (Thinking)`</t>
+          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
+ البديل: `Gemini 2.0 Pro Experimental`</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -694,8 +694,8 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.1 Pro (High)` 
- البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+          <t>الأساسي: `Claude 3.5 Sonnet` 
+ البديل: `Gemini 2.0 Pro`</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -734,8 +734,8 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.1 Pro (High)` 
- البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
+ البديل: `Gemini 2.0 Flash`</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -773,8 +773,8 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.1 Pro (High)` 
- البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
+ البديل: `Gemini 2.0 Pro`</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -812,8 +812,8 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.1 Pro (Low)` 
- البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+          <t>الأساسي: `Gemini 2.0 Flash` 
+ البديل: `Claude 3.5 Haiku`</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -851,8 +851,8 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.1 Pro (High)` 
- البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
+ البديل: `Gemini 2.0 Pro`</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -891,8 +891,8 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.1 Pro (High)` 
- البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
+ البديل: `Gemini 2.0 Pro`</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -930,8 +930,8 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.1 Pro (High)` 
- البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+          <t>الأساسي: `Gemini 2.0 Flash` 
+ البديل: `Claude 3.5 Haiku`</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -969,8 +969,8 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.1 Pro (High)` 
- البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+          <t>الأساسي: `Claude 3.5 Sonnet` 
+ البديل: `Gemini 2.0 Flash`</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1009,8 +1009,8 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
- البديل: `Gemini 3.1 Pro (High)`</t>
+          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
+ البديل: `Gemini 2.0 Pro (Thinking)`</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1050,8 +1050,8 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
- البديل: `Gemini 3.1 Pro (High)`</t>
+          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
+ البديل: `Gemini 2.0 Pro`</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1090,8 +1090,8 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.1 Pro (High)` 
- البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+          <t>الأساسي: `Gemini 2.0 Flash` 
+ البديل: `Claude 3.5 Haiku`</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1129,8 +1129,8 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.6 Flash (Medium)` 
- البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+          <t>الأساسي: `Gemini 2.0 Flash` 
+ البديل: `Claude 3.5 Haiku`</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1168,8 +1168,8 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.6 Flash (Low)` 
- البديل: `Gemini 3.5 Flash (Low)`</t>
+          <t>الأساسي: `Gemini 2.0 Flash` 
+ البديل: `Claude 3.5 Haiku`</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1208,8 +1208,8 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.1 Pro (High)` 
- البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
+ البديل: `Gemini 2.0 Pro (Thinking)`</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1248,8 +1248,8 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
- البديل: `Gemini 3.1 Pro (High)`</t>
+          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
+ البديل: `Gemini 2.0 Pro`</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1350,8 +1350,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.1 Pro (High)` 
- البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
+ البديل: `Gemini 2.0 Pro`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1450,8 +1450,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.1 Pro (High)` 
- البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
+ البديل: `Gemini 2.0 Pro`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1549,8 +1549,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.1 Pro (High)` 
- البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+          <t>الأساسي: `Gemini 2.0 Flash` 
+ البديل: `Claude 3.5 Haiku`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1648,8 +1648,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.1 Pro (High)` 
- البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+          <t>الأساسي: `Claude 3.5 Sonnet` 
+ البديل: `Gemini 2.0 Flash`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1748,8 +1748,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
- البديل: `Gemini 3.1 Pro (High)`</t>
+          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
+ البديل: `Gemini 2.0 Pro (Thinking)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1849,8 +1849,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
- البديل: `Gemini 3.1 Pro (High)`</t>
+          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
+ البديل: `Gemini 2.0 Pro`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1949,8 +1949,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.1 Pro (High)` 
- البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+          <t>الأساسي: `Gemini 2.0 Flash` 
+ البديل: `Claude 3.5 Haiku`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2048,8 +2048,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.6 Flash (Medium)` 
- البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+          <t>الأساسي: `Gemini 2.0 Flash` 
+ البديل: `Claude 3.5 Haiku`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2147,8 +2147,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.6 Flash (Low)` 
- البديل: `Gemini 3.5 Flash (Low)`</t>
+          <t>الأساسي: `Gemini 2.0 Flash` 
+ البديل: `Claude 3.5 Haiku`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2247,8 +2247,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.1 Pro (High)` 
- البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
+ البديل: `Gemini 2.0 Pro (Thinking)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2347,8 +2347,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.6 Flash (Medium)` 
- البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+          <t>الأساسي: `Gemini 2.0 Flash` 
+ البديل: `Claude 3.5 Haiku`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2446,8 +2446,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
- البديل: `Gemini 3.1 Pro (High)`</t>
+          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
+ البديل: `Gemini 2.0 Pro`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2548,8 +2548,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
- البديل: `Claude Opus 4.6 (Thinking)`</t>
+          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
+ البديل: `Gemini 2.0 Pro`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2648,8 +2648,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
- البديل: `Gemini 3.1 Pro (High)`</t>
+          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
+ البديل: `Gemini 2.0 Pro (Thinking)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2748,8 +2748,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.1 Pro (High)` 
- البديل: `Claude Opus 4.6 (Thinking)`</t>
+          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
+ البديل: `Gemini 2.0 Pro Experimental`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2850,8 +2850,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.1 Pro (High)` 
- البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+          <t>الأساسي: `Claude 3.5 Sonnet` 
+ البديل: `Gemini 2.0 Pro`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2950,8 +2950,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.1 Pro (High)` 
- البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
+ البديل: `Gemini 2.0 Flash`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -3049,8 +3049,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.1 Pro (High)` 
- البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
+ البديل: `Gemini 2.0 Pro`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -3148,8 +3148,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.1 Pro (Low)` 
- البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+          <t>الأساسي: `Gemini 2.0 Flash` 
+ البديل: `Claude 3.5 Haiku`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">

--- a/HOOKS_GUIDE.xlsx
+++ b/HOOKS_GUIDE.xlsx
@@ -533,8 +533,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 2.0 Flash` 
- البديل: `Claude 3.5 Haiku`</t>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Gemini 3.6 Flash (Medium)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -572,8 +572,8 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
- البديل: `Gemini 2.0 Pro`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Claude Opus 4.6 (Thinking)`</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -612,8 +612,8 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
- البديل: `Gemini 2.0 Pro (Thinking)`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -652,8 +652,8 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
- البديل: `Gemini 2.0 Pro Experimental`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Claude Opus 4.6 (Thinking)`</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -694,8 +694,8 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude 3.5 Sonnet` 
- البديل: `Gemini 2.0 Pro`</t>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Claude Sonnet 4.6 (Thinking)`</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -734,8 +734,8 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
- البديل: `Gemini 2.0 Flash`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -773,8 +773,8 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
- البديل: `Gemini 2.0 Pro`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Claude Opus 4.6 (Thinking)`</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -812,8 +812,8 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 2.0 Flash` 
- البديل: `Claude 3.5 Haiku`</t>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Gemini 3.6 Flash (Medium)`</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -851,8 +851,8 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
- البديل: `Gemini 2.0 Pro`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -891,8 +891,8 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
- البديل: `Gemini 2.0 Pro`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -930,8 +930,8 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 2.0 Flash` 
- البديل: `Claude 3.5 Haiku`</t>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Gemini 3.6 Flash (Medium)`</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -969,8 +969,8 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude 3.5 Sonnet` 
- البديل: `Gemini 2.0 Flash`</t>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Claude Sonnet 4.6 (Thinking)`</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1009,8 +1009,8 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
- البديل: `Gemini 2.0 Pro (Thinking)`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `GPT-OSS 120B (Medium)`</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1050,8 +1050,8 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
- البديل: `Gemini 2.0 Pro`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1090,8 +1090,8 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 2.0 Flash` 
- البديل: `Claude 3.5 Haiku`</t>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Gemini 3.6 Flash (Medium)`</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1129,8 +1129,8 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 2.0 Flash` 
- البديل: `Claude 3.5 Haiku`</t>
+          <t>الأساسي: `Gemini 3.6 Flash (Medium)` 
+ البديل: `Gemini 3.5 Flash (Medium)`</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1168,8 +1168,8 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 2.0 Flash` 
- البديل: `Claude 3.5 Haiku`</t>
+          <t>الأساسي: `Gemini 3.5 Flash (Medium)` 
+ البديل: `Gemini 3.1 Pro (Low)`</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1208,8 +1208,8 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
- البديل: `Gemini 2.0 Pro (Thinking)`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Claude Opus 4.6 (Thinking)`</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1248,8 +1248,8 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
- البديل: `Gemini 2.0 Pro`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1350,8 +1350,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
- البديل: `Gemini 2.0 Pro`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1450,8 +1450,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
- البديل: `Gemini 2.0 Pro`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1549,8 +1549,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 2.0 Flash` 
- البديل: `Claude 3.5 Haiku`</t>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Gemini 3.6 Flash (Medium)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1648,8 +1648,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude 3.5 Sonnet` 
- البديل: `Gemini 2.0 Flash`</t>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Claude Sonnet 4.6 (Thinking)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1748,8 +1748,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
- البديل: `Gemini 2.0 Pro (Thinking)`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `GPT-OSS 120B (Medium)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1849,8 +1849,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
- البديل: `Gemini 2.0 Pro`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1949,8 +1949,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 2.0 Flash` 
- البديل: `Claude 3.5 Haiku`</t>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Gemini 3.6 Flash (Medium)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2048,8 +2048,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 2.0 Flash` 
- البديل: `Claude 3.5 Haiku`</t>
+          <t>الأساسي: `Gemini 3.6 Flash (Medium)` 
+ البديل: `Gemini 3.5 Flash (Medium)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2147,8 +2147,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 2.0 Flash` 
- البديل: `Claude 3.5 Haiku`</t>
+          <t>الأساسي: `Gemini 3.5 Flash (Medium)` 
+ البديل: `Gemini 3.1 Pro (Low)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2247,8 +2247,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
- البديل: `Gemini 2.0 Pro (Thinking)`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Claude Opus 4.6 (Thinking)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2347,8 +2347,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 2.0 Flash` 
- البديل: `Claude 3.5 Haiku`</t>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Gemini 3.6 Flash (Medium)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2446,8 +2446,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
- البديل: `Gemini 2.0 Pro`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2548,8 +2548,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
- البديل: `Gemini 2.0 Pro`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Claude Opus 4.6 (Thinking)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2648,8 +2648,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
- البديل: `Gemini 2.0 Pro (Thinking)`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2748,8 +2748,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
- البديل: `Gemini 2.0 Pro Experimental`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Claude Opus 4.6 (Thinking)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2850,8 +2850,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude 3.5 Sonnet` 
- البديل: `Gemini 2.0 Pro`</t>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Claude Sonnet 4.6 (Thinking)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2950,8 +2950,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
- البديل: `Gemini 2.0 Flash`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -3049,8 +3049,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude 3.7 Sonnet (Thinking)` 
- البديل: `Gemini 2.0 Pro`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Claude Opus 4.6 (Thinking)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -3148,8 +3148,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 2.0 Flash` 
- البديل: `Claude 3.5 Haiku`</t>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Gemini 3.6 Flash (Medium)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">

--- a/HOOKS_GUIDE.xlsx
+++ b/HOOKS_GUIDE.xlsx
@@ -802,12 +802,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>8. خطاف مراجعة وتحديث المكتبات</t>
+          <t>8. خطاف مراجعة وتحديث المكتبات والنماذج</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>تحديث الاعتماديات, تحديث المكتبات</t>
+          <t>تحديث الاعتماديات, تحديث المكتبات, تحديث النماذج, معايرة النماذج, update models</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -818,20 +818,28 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>[github-talent-scout], [code-architect]</t>
+          <t>[github-talent-scout], [code-architect], [agent-optimizer]</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>فحص ملفات Gradle وتحديث المكتبات والاعتماديات القديمة وتجنب التعارضات.</t>
+          <t>فحص ملفات Gradle وتحديث المكتبات، والتحقق التلقائي عبر الإنترنت (antigravity.google) لتحديث مصفوفة النماذج دون لقطات شاشة.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **فحص الإصدارات:** مسح ملفات `build.gradle.kts` ومقارنة إصدارات المكتبات الحالية بأحدث الإصدارات المستقرة.
-  2. **التحقق من التوافق:** دراسة التغييرات الجوهرية (Breaking Changes) في المكتبات المحدثة لضمان عدم كسر الكود الحالي.
-  3. **التحديث الآمن:** ترقية المكتبات تدريجياً واختبار البناء بعد كل ترقية.</t>
+  1. **فحص إصدارات المكتبات:** مسح ملفات `build.gradle.kts` ومقارنة إصدارات المكتبات الحالية بأحدث الإصدارات المستقرة.
+  2. **الاستكشاف والمعايرة التلقائية للنماذج عبر الإنترنت (Online Model Discovery):**
+     - عند كتابة محفز `"تحديث النماذج"` أو `"معايرة النماذج"`، يقوم الوكيل `[agent-optimizer]` بالاستعلام الفوري عبر الإنترنت من المصادر الرسمية:
+       - 🌐 بوابة Google Antigravity الرسمية: `https://antigravity.google`
+       - 🌐 مدونة مطوري جوجل: `https://google.dev` و `https://blog.google`
+       - 🌐 دليل وثائق Anthropic: `https://docs.anthropic.com`
+     - يتم استخراج قائمة النماذج الفعالة في المحرر (مثل `Gemini 3.7 Flash`, `Claude Sonnet 4.6 (Thinking)`).
+  3. **التحديث والمزامنة الشاملة:**
+     - تحديث مصفوفة النماذج في `HOOKS_GUIDE.md`.
+     - تشغيل السكربتات لتحديث ملف الإكسيل `HOOKS_GUIDE.xlsx` وتطبيق مكتبة الأوامر HTML.
+     - تشغيل `sync_global_ecosystem.py` ورفع التحديثات لـ GitHub تلقائياً.</t>
         </is>
       </c>
     </row>
@@ -3138,12 +3146,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>8. خطاف مراجعة وتحديث المكتبات</t>
+          <t>8. خطاف مراجعة وتحديث المكتبات والنماذج</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>تحديث الاعتماديات, تحديث المكتبات</t>
+          <t>تحديث الاعتماديات, تحديث المكتبات, تحديث النماذج, معايرة النماذج, update models</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -3154,20 +3162,28 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[github-talent-scout], [code-architect]</t>
+          <t>[github-talent-scout], [code-architect], [agent-optimizer]</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>فحص ملفات Gradle وتحديث المكتبات والاعتماديات القديمة وتجنب التعارضات.</t>
+          <t>فحص ملفات Gradle وتحديث المكتبات، والتحقق التلقائي عبر الإنترنت (antigravity.google) لتحديث مصفوفة النماذج دون لقطات شاشة.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **فحص الإصدارات:** مسح ملفات `build.gradle.kts` ومقارنة إصدارات المكتبات الحالية بأحدث الإصدارات المستقرة.
-  2. **التحقق من التوافق:** دراسة التغييرات الجوهرية (Breaking Changes) في المكتبات المحدثة لضمان عدم كسر الكود الحالي.
-  3. **التحديث الآمن:** ترقية المكتبات تدريجياً واختبار البناء بعد كل ترقية.</t>
+  1. **فحص إصدارات المكتبات:** مسح ملفات `build.gradle.kts` ومقارنة إصدارات المكتبات الحالية بأحدث الإصدارات المستقرة.
+  2. **الاستكشاف والمعايرة التلقائية للنماذج عبر الإنترنت (Online Model Discovery):**
+     - عند كتابة محفز `"تحديث النماذج"` أو `"معايرة النماذج"`، يقوم الوكيل `[agent-optimizer]` بالاستعلام الفوري عبر الإنترنت من المصادر الرسمية:
+       - 🌐 بوابة Google Antigravity الرسمية: `https://antigravity.google`
+       - 🌐 مدونة مطوري جوجل: `https://google.dev` و `https://blog.google`
+       - 🌐 دليل وثائق Anthropic: `https://docs.anthropic.com`
+     - يتم استخراج قائمة النماذج الفعالة في المحرر (مثل `Gemini 3.7 Flash`, `Claude Sonnet 4.6 (Thinking)`).
+  3. **التحديث والمزامنة الشاملة:**
+     - تحديث مصفوفة النماذج في `HOOKS_GUIDE.md`.
+     - تشغيل السكربتات لتحديث ملف الإكسيل `HOOKS_GUIDE.xlsx` وتطبيق مكتبة الأوامر HTML.
+     - تشغيل `sync_global_ecosystem.py` ورفع التحديثات لـ GitHub تلقائياً.</t>
         </is>
       </c>
     </row>

--- a/HOOKS_GUIDE.xlsx
+++ b/HOOKS_GUIDE.xlsx
@@ -823,7 +823,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>فحص ملفات Gradle وتحديث المكتبات، والتحقق التلقائي عبر الإنترنت (antigravity.google) لتحديث مصفوفة النماذج دون لقطات شاشة.</t>
+          <t>فحص ملفات Gradle وتحديث المكتبات، والتحقق التلقائي عبر الإنترنت (antigravity.google) لتحديث مصفوفة النماذج ودليل hooks_user_guide.md دون لقطات شاشة.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
        - 🌐 دليل وثائق Anthropic: `https://docs.anthropic.com`
      - يتم استخراج قائمة النماذج الفعالة في المحرر (مثل `Gemini 3.7 Flash`, `Claude Sonnet 4.6 (Thinking)`).
   3. **التحديث والمزامنة الشاملة:**
-     - تحديث مصفوفة النماذج في `HOOKS_GUIDE.md`.
+     - تحديث مصفوفة النماذج في `HOOKS_GUIDE.md` ودليل مسار العمل `hooks_user_guide.md`.
      - تشغيل السكربتات لتحديث ملف الإكسيل `HOOKS_GUIDE.xlsx` وتطبيق مكتبة الأوامر HTML.
      - تشغيل `sync_global_ecosystem.py` ورفع التحديثات لـ GitHub تلقائياً.</t>
         </is>
@@ -988,7 +988,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>صياغة التعديلات كإنجازات ومطابقتها برمجياً عبر docs-guard ثم كتابتها في README.md ورفعها لـ GitHub.</t>
+          <t>صياغة التعديلات كإنجازات ومطابقتها برمجياً وتحديث README.md و hooks_user_guide.md ثم الرفع لـ GitHub.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -996,8 +996,8 @@
           <t>* **طريقة العمل والإجراءات:**
   1. **قراءة السجل والذاكرة:** مراجعة التغييرات الأخيرة في الملفات وقراءة `MEMORY_STORE.md` لاستخلاص ما تم إنجازه.
   2. **مطابقة التوثيق (`docs-guard`):** مطابقة كل رمز برمجي أو مسار أو دالة مذكورة في التوثيق مع الكود الحقيقي لمنع أي تباين أو اختلاق (Docs-vs-Code Drift).
-  3. **صياغة الإنجازات وتحديث README:** كتابة الإنجازات بنسق احترافي كنقاط موجزة، وإضافتها إلى ملف `README.md` الخاص بالمشروع.
-  4. **الرفع التلقائي (Commit &amp; Push):** إضافة التعديل على `README.md` وإجراء عملية الحفظ، ثم الرفع التلقائي إلى GitHub مباشرة كخطوة نهائية متصلة.</t>
+  3. **صياغة الإنجازات وتحديث التوثيق:** كتابة الإنجازات بنسق احترافي كنقاط موجزة، وتحديث ملف `README.md` وملف [`hooks_user_guide.md`](file:///f:/AI%20PROJECTS/Blind%20App/hooks_user_guide.md).
+  4. **الرفع التلقائي (Commit &amp; Push):** إضافة التعديلات وإجراء الحفظ، ثم الرفع التلقائي إلى GitHub مباشرة كخطوة نهائية متصلة.</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>تحليل المستودعات الخارجية واستيراد المهارات وتعميمها وتحديث الخطافات والإكسيل وتطبيق مكتبة الأوامر ومزامنة المنظومة.</t>
+          <t>تحليل المستودعات الخارجية واستيراد المهارات وتعميمها وتحديث الخطافات والإكسيل وتطبيق مكتبة الأوامر ودليل hooks_user_guide.md ومزامنة المنظومة.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
   1. **فحص وتقييم المورد (`resource-scout-integrator` + `github-talent-scout`):** استلام رابط المستودع الخارجي وفحص ملفات README والأكواد وتحديد ما إذا كان يُحدث نقلة نوعية واستبعاد ما لا يتوافق مع البيئة.
   2. **بناء وهيكلة المهارات (`skill-forge-builder`):** استخراج المهارات الفعالة وصياغة ملفات `SKILL.md` وفق المعايير العالمية.
   3. **التعميم العالمي (`global-deployment`):** نشر المهارات في `C:\Users\Kt\.gemini\config\skills/` لتصبح متاحة لكل المشاريع.
-  4. **تحديث الخطافات والإكسيل وتطبيق مكتبة الأوامر (`agent-optimizer` + `frontend-design-builder`):** إضافة المهارات للخطافات ذات الصلة وتشغيل سكربت `convert_hooks_to_sheets.py` لتحديث ملف الإكسيل `HOOKS_GUIDE.xlsx` وتشغيل `update_html.py` لتحديث تطبيق مكتبة الأوامر التفاعلي (`03_Dynamic_Prompt_Library/index.html`).
+  4. **تحديث الخطافات والإكسيل وتطبيق مكتبة الأوامر ودليل المستخدم (`agent-optimizer` + `frontend-design-builder`):** إضافة المهارات للخطافات ذات الصلة، وتحديث `hooks_user_guide.md` و `USER_GUIDE.md`، وتشغيل سكربت `convert_hooks_to_sheets.py` لتحديث ملف الإكسيل `HOOKS_GUIDE.xlsx` وتشغيل `update_html.py` لتحديث تطبيق مكتبة الأوامر التفاعلي (`03_Dynamic_Prompt_Library/index.html`).
   5. **مزامنة المستودع العام سحابياً (`git-github-manager`):** تشغيل `sync_global_ecosystem.py` لمزامنة كامل منظومة الوكلاء والمهارات والدليل مع مستودع `Claude-Antigravity-Workspace` ورفعه إلى GitHub.
 &lt;/div&gt;</t>
         </is>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>صياغة التعديلات كإنجازات ومطابقتها برمجياً عبر docs-guard ثم كتابتها في README.md ورفعها لـ GitHub.</t>
+          <t>صياغة التعديلات كإنجازات ومطابقتها برمجياً وتحديث README.md و hooks_user_guide.md ثم الرفع لـ GitHub.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1675,8 +1675,8 @@
           <t>* **طريقة العمل والإجراءات:**
   1. **قراءة السجل والذاكرة:** مراجعة التغييرات الأخيرة في الملفات وقراءة `MEMORY_STORE.md` لاستخلاص ما تم إنجازه.
   2. **مطابقة التوثيق (`docs-guard`):** مطابقة كل رمز برمجي أو مسار أو دالة مذكورة في التوثيق مع الكود الحقيقي لمنع أي تباين أو اختلاق (Docs-vs-Code Drift).
-  3. **صياغة الإنجازات وتحديث README:** كتابة الإنجازات بنسق احترافي كنقاط موجزة، وإضافتها إلى ملف `README.md` الخاص بالمشروع.
-  4. **الرفع التلقائي (Commit &amp; Push):** إضافة التعديل على `README.md` وإجراء عملية الحفظ، ثم الرفع التلقائي إلى GitHub مباشرة كخطوة نهائية متصلة.</t>
+  3. **صياغة الإنجازات وتحديث التوثيق:** كتابة الإنجازات بنسق احترافي كنقاط موجزة، وتحديث ملف `README.md` وملف [`hooks_user_guide.md`](file:///f:/AI%20PROJECTS/Blind%20App/hooks_user_guide.md).
+  4. **الرفع التلقائي (Commit &amp; Push):** إضافة التعديلات وإجراء الحفظ، ثم الرفع التلقائي إلى GitHub مباشرة كخطوة نهائية متصلة.</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>تحليل المستودعات الخارجية واستيراد المهارات وتعميمها وتحديث الخطافات والإكسيل وتطبيق مكتبة الأوامر ومزامنة المنظومة.</t>
+          <t>تحليل المستودعات الخارجية واستيراد المهارات وتعميمها وتحديث الخطافات والإكسيل وتطبيق مكتبة الأوامر ودليل hooks_user_guide.md ومزامنة المنظومة.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
   1. **فحص وتقييم المورد (`resource-scout-integrator` + `github-talent-scout`):** استلام رابط المستودع الخارجي وفحص ملفات README والأكواد وتحديد ما إذا كان يُحدث نقلة نوعية واستبعاد ما لا يتوافق مع البيئة.
   2. **بناء وهيكلة المهارات (`skill-forge-builder`):** استخراج المهارات الفعالة وصياغة ملفات `SKILL.md` وفق المعايير العالمية.
   3. **التعميم العالمي (`global-deployment`):** نشر المهارات في `C:\Users\Kt\.gemini\config\skills/` لتصبح متاحة لكل المشاريع.
-  4. **تحديث الخطافات والإكسيل وتطبيق مكتبة الأوامر (`agent-optimizer` + `frontend-design-builder`):** إضافة المهارات للخطافات ذات الصلة وتشغيل سكربت `convert_hooks_to_sheets.py` لتحديث ملف الإكسيل `HOOKS_GUIDE.xlsx` وتشغيل `update_html.py` لتحديث تطبيق مكتبة الأوامر التفاعلي (`03_Dynamic_Prompt_Library/index.html`).
+  4. **تحديث الخطافات والإكسيل وتطبيق مكتبة الأوامر ودليل المستخدم (`agent-optimizer` + `frontend-design-builder`):** إضافة المهارات للخطافات ذات الصلة، وتحديث `hooks_user_guide.md` و `USER_GUIDE.md`، وتشغيل سكربت `convert_hooks_to_sheets.py` لتحديث ملف الإكسيل `HOOKS_GUIDE.xlsx` وتشغيل `update_html.py` لتحديث تطبيق مكتبة الأوامر التفاعلي (`03_Dynamic_Prompt_Library/index.html`).
   5. **مزامنة المستودع العام سحابياً (`git-github-manager`):** تشغيل `sync_global_ecosystem.py` لمزامنة كامل منظومة الوكلاء والمهارات والدليل مع مستودع `Claude-Antigravity-Workspace` ورفعه إلى GitHub.
 &lt;/div&gt;</t>
         </is>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>فحص ملفات Gradle وتحديث المكتبات، والتحقق التلقائي عبر الإنترنت (antigravity.google) لتحديث مصفوفة النماذج دون لقطات شاشة.</t>
+          <t>فحص ملفات Gradle وتحديث المكتبات، والتحقق التلقائي عبر الإنترنت (antigravity.google) لتحديث مصفوفة النماذج ودليل hooks_user_guide.md دون لقطات شاشة.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -3181,7 +3181,7 @@
        - 🌐 دليل وثائق Anthropic: `https://docs.anthropic.com`
      - يتم استخراج قائمة النماذج الفعالة في المحرر (مثل `Gemini 3.7 Flash`, `Claude Sonnet 4.6 (Thinking)`).
   3. **التحديث والمزامنة الشاملة:**
-     - تحديث مصفوفة النماذج في `HOOKS_GUIDE.md`.
+     - تحديث مصفوفة النماذج في `HOOKS_GUIDE.md` ودليل مسار العمل `hooks_user_guide.md`.
      - تشغيل السكربتات لتحديث ملف الإكسيل `HOOKS_GUIDE.xlsx` وتطبيق مكتبة الأوامر HTML.
      - تشغيل `sync_global_ecosystem.py` ورفع التحديثات لـ GitHub تلقائياً.</t>
         </is>

--- a/HOOKS_GUIDE.xlsx
+++ b/HOOKS_GUIDE.xlsx
@@ -27,6 +27,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17. خطاف إدارة تليجرام" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18. خطاف التدقيق البرمجي الشا" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19. خطاف استكشاف وتكامل الموا" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20. خطاف المزامنة السحابية ال" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1277,7 +1278,47 @@
   2. **بناء وهيكلة المهارات (`skill-forge-builder`):** استخراج المهارات الفعالة وصياغة ملفات `SKILL.md` وفق المعايير العالمية.
   3. **التعميم العالمي (`global-deployment`):** نشر المهارات في `C:\Users\Kt\.gemini\config\skills/` لتصبح متاحة لكل المشاريع.
   4. **تحديث الخطافات والإكسيل وتطبيق مكتبة الأوامر ودليل المستخدم (`agent-optimizer` + `frontend-design-builder`):** إضافة المهارات للخطافات ذات الصلة، وتحديث `hooks_user_guide.md` و `USER_GUIDE.md`، وتشغيل سكربت `convert_hooks_to_sheets.py` لتحديث ملف الإكسيل `HOOKS_GUIDE.xlsx` وتشغيل `update_html.py` لتحديث تطبيق مكتبة الأوامر التفاعلي (`03_Dynamic_Prompt_Library/index.html`).
-  5. **مزامنة المستودع العام سحابياً (`git-github-manager`):** تشغيل `sync_global_ecosystem.py` لمزامنة كامل منظومة الوكلاء والمهارات والدليل مع مستودع `Claude-Antigravity-Workspace` ورفعه إلى GitHub.
+  5. **مزامنة المستودع العام سحابياً (`git-github-manager`):** تشغيل `sync_global_ecosystem.py` لمزامنة كامل منظومة الوكلاء والمهارات والدليل مع مستودع `Claude-Antigravity-Workspace` ورفعه إلى GitHub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>20. خطاف المزامنة السحابية الشاملة للمنظومة</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>مزامنة عالمية, مزامنة المنظومة, مزامنة المستودع, تحديث السحابة, sync ecosystem, global sync</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>[resource-scout-integrator], [git-github-manager], [agent-optimizer], [frontend-design-builder]</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>مزامنة 100% لكافة المكونات العالمية (المهارات، الوكلاء، الإضافات، المراجع، الإكسيل، وتطبيق HTML) ورفعها لمستودع Claude-Antigravity-Workspace على GitHub.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **تحديث مصنف الإكسيل وتطبيق الأوامر:** تشغيل `convert_hooks_to_sheets.py` لتحديث ملف الإكسيل التفاعلي `HOOKS_GUIDE.xlsx` وتشغيل `update_html.py` لتحديث تطبيق مكتبة الأوامر الذكية `index.html`.
+  2. **مزامنة المهارات والوكلاء والإضافات العالمية:** نسخ كافة المهارات (80+) والوكلاء (25+) والإضافات الـ 8 (`plugins/`) والمراجع وبذور المشاريع وإعدادات MCP من مسارات النظام العالمي (`~/.gemini/config/`) والمحلي إلى مستودع المنظومة.
+  3. **مطابقة وتحديث أدلة المستخدم:** تحديث `hooks_user_guide.md` و `USER_GUIDE.md` و `README.md` لتعكس كافة الإضافات والترقيات الحديثة.
+  4. **الالتزام والدفع السحابي إلى GitHub:** تنفيذ `git commit` موثق ودفع كافة الملفات والمجلدات إلى مستودع [Claude-Antigravity-Workspace](https://github.com/ibrahimalkateb965-tech/Claude-Antigravity-Workspace) على GitHub بنقرة واحدة وإصدار تقرير النجاح.
 &lt;/div&gt;</t>
         </is>
       </c>
@@ -2475,7 +2516,107 @@
   2. **بناء وهيكلة المهارات (`skill-forge-builder`):** استخراج المهارات الفعالة وصياغة ملفات `SKILL.md` وفق المعايير العالمية.
   3. **التعميم العالمي (`global-deployment`):** نشر المهارات في `C:\Users\Kt\.gemini\config\skills/` لتصبح متاحة لكل المشاريع.
   4. **تحديث الخطافات والإكسيل وتطبيق مكتبة الأوامر ودليل المستخدم (`agent-optimizer` + `frontend-design-builder`):** إضافة المهارات للخطافات ذات الصلة، وتحديث `hooks_user_guide.md` و `USER_GUIDE.md`، وتشغيل سكربت `convert_hooks_to_sheets.py` لتحديث ملف الإكسيل `HOOKS_GUIDE.xlsx` وتشغيل `update_html.py` لتحديث تطبيق مكتبة الأوامر التفاعلي (`03_Dynamic_Prompt_Library/index.html`).
-  5. **مزامنة المستودع العام سحابياً (`git-github-manager`):** تشغيل `sync_global_ecosystem.py` لمزامنة كامل منظومة الوكلاء والمهارات والدليل مع مستودع `Claude-Antigravity-Workspace` ورفعه إلى GitHub.
+  5. **مزامنة المستودع العام سحابياً (`git-github-manager`):** تشغيل `sync_global_ecosystem.py` لمزامنة كامل منظومة الوكلاء والمهارات والدليل مع مستودع `Claude-Antigravity-Workspace` ورفعه إلى GitHub.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>20. خطاف المزامنة السحابية الشاملة للمنظومة</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>مزامنة عالمية, مزامنة المنظومة, مزامنة المستودع, تحديث السحابة, sync ecosystem, global sync</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[resource-scout-integrator], [git-github-manager], [agent-optimizer], [frontend-design-builder]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>مزامنة 100% لكافة المكونات العالمية (المهارات، الوكلاء، الإضافات، المراجع، الإكسيل، وتطبيق HTML) ورفعها لمستودع Claude-Antigravity-Workspace على GitHub.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **تحديث مصنف الإكسيل وتطبيق الأوامر:** تشغيل `convert_hooks_to_sheets.py` لتحديث ملف الإكسيل التفاعلي `HOOKS_GUIDE.xlsx` وتشغيل `update_html.py` لتحديث تطبيق مكتبة الأوامر الذكية `index.html`.
+  2. **مزامنة المهارات والوكلاء والإضافات العالمية:** نسخ كافة المهارات (80+) والوكلاء (25+) والإضافات الـ 8 (`plugins/`) والمراجع وبذور المشاريع وإعدادات MCP من مسارات النظام العالمي (`~/.gemini/config/`) والمحلي إلى مستودع المنظومة.
+  3. **مطابقة وتحديث أدلة المستخدم:** تحديث `hooks_user_guide.md` و `USER_GUIDE.md` و `README.md` لتعكس كافة الإضافات والترقيات الحديثة.
+  4. **الالتزام والدفع السحابي إلى GitHub:** تنفيذ `git commit` موثق ودفع كافة الملفات والمجلدات إلى مستودع [Claude-Antigravity-Workspace](https://github.com/ibrahimalkateb965-tech/Claude-Antigravity-Workspace) على GitHub بنقرة واحدة وإصدار تقرير النجاح.
 &lt;/div&gt;</t>
         </is>
       </c>

--- a/HOOKS_GUIDE.xlsx
+++ b/HOOKS_GUIDE.xlsx
@@ -1275,7 +1275,7 @@
         <is>
           <t>* **طريقة العمل والإجراءات:**
   1. **فحص وتقييم المورد (`resource-scout-integrator` + `github-talent-scout`):** استلام رابط المستودع الخارجي وفحص ملفات README والأكواد وتحديد ما إذا كان يُحدث نقلة نوعية واستبعاد ما لا يتوافق مع البيئة.
-  2. **بناء وهيكلة المهارات (`skill-forge-builder`):** استخراج المهارات الفعالة وصياغة ملفات `SKILL.md` وفق المعايير العالمية.
+  2. **بناء وهيكلة المهارات (`skill-forge-builder`):** استخراج المهارات الفعالة وصياغة ملفات `SKILL.md` وفق المعايير العالمية عبر `skill-creator` و `find-skills`.
   3. **التعميم العالمي (`global-deployment`):** نشر المهارات في `C:\Users\Kt\.gemini\config\skills/` لتصبح متاحة لكل المشاريع.
   4. **تحديث الخطافات والإكسيل وتطبيق مكتبة الأوامر ودليل المستخدم (`agent-optimizer` + `frontend-design-builder`):** إضافة المهارات للخطافات ذات الصلة، وتحديث `hooks_user_guide.md` و `USER_GUIDE.md`، وتشغيل سكربت `convert_hooks_to_sheets.py` لتحديث ملف الإكسيل `HOOKS_GUIDE.xlsx` وتشغيل `update_html.py` لتحديث تطبيق مكتبة الأوامر التفاعلي (`03_Dynamic_Prompt_Library/index.html`).
   5. **مزامنة المستودع العام سحابياً (`git-github-manager`):** تشغيل `sync_global_ecosystem.py` لمزامنة كامل منظومة الوكلاء والمهارات والدليل مع مستودع `Claude-Antigravity-Workspace` ورفعه إلى GitHub.</t>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>20. خطاف المزامنة السحابية الشاملة للمنظومة</t>
+          <t>20. خطاف المزامنة السحابية الشاملة ومطابقة المنظومة</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>مزامنة عالمية, مزامنة المنظومة, مزامنة المستودع, تحديث السحابة, sync ecosystem, global sync</t>
+          <t>مزامنة المنظومة, مزامنة المستودع العام, تحديث المنظومة العالمية, sync ecosystem, sync workspace</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1304,21 +1304,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>[resource-scout-integrator], [git-github-manager], [agent-optimizer], [frontend-design-builder]</t>
+          <t>[git-github-manager], [persistent-memory-engine], [agent-optimizer], [docs-guard]</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>مزامنة 100% لكافة المكونات العالمية (المهارات، الوكلاء، الإضافات، المراجع، الإكسيل، وتطبيق HTML) ورفعها لمستودع Claude-Antigravity-Workspace على GitHub.</t>
+          <t>مطابقة ومزامنة كافة الإضافات (Plugins)، المراجع والذاكرة، إعدادات MCP، المهارات والوكلاء، وتحديث الإكسيل ومكتبة الأوامر، ورفعها لـ GitHub بتطابق 100%.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **تحديث مصنف الإكسيل وتطبيق الأوامر:** تشغيل `convert_hooks_to_sheets.py` لتحديث ملف الإكسيل التفاعلي `HOOKS_GUIDE.xlsx` وتشغيل `update_html.py` لتحديث تطبيق مكتبة الأوامر الذكية `index.html`.
-  2. **مزامنة المهارات والوكلاء والإضافات العالمية:** نسخ كافة المهارات (80+) والوكلاء (25+) والإضافات الـ 8 (`plugins/`) والمراجع وبذور المشاريع وإعدادات MCP من مسارات النظام العالمي (`~/.gemini/config/`) والمحلي إلى مستودع المنظومة.
-  3. **مطابقة وتحديث أدلة المستخدم:** تحديث `hooks_user_guide.md` و `USER_GUIDE.md` و `README.md` لتعكس كافة الإضافات والترقيات الحديثة.
-  4. **الالتزام والدفع السحابي إلى GitHub:** تنفيذ `git commit` موثق ودفع كافة الملفات والمجلدات إلى مستودع [Claude-Antigravity-Workspace](https://github.com/ibrahimalkateb965-tech/Claude-Antigravity-Workspace) على GitHub بنقرة واحدة وإصدار تقرير النجاح.
+  1. **التحقق من سلامة المكونات والبيئة (`agent-optimizer`):** فحص حزم الإضافات (Plugins)، المهارات، والوكلاء والتكوينات العالمية في `~/.gemini/config/` ومقارنتها بالمشروع.
+  2. **تحديث ملفات الإكسيل وتطبيق مكتبة الأوامر:** تشغيل `convert_hooks_to_sheets.py` و `update_html.py` لتحديث `HOOKS_GUIDE.xlsx` و `index.html` بكافة الخطافات وتفاصيلها.
+  3. **تشغيل محرك المزامنة الشاملة (`sync_global_ecosystem.py`):** نسخ ومطابقة كافة الإضافات (Plugins)، والمراجع والذاكرة (References)، والمهارات، والوكلاء، وإعدادات MCP إلى `Claude-Antigravity-Workspace` بضمان تطابق 100%.
+  4. **فحص ومطابقة التوثيق (`docs-guard`):** مراجعة سلامة `README.md`, `USER_GUIDE.md`, `hooks_user_guide.md` لضمان عدم وجود أي انحراف.
+  5. **الالتزام والرفع التلقائي إلى GitHub (`git-github-manager`):** تنفيذ `git commit` موثق ودفع كافة التحديثات إلى المستودع العام [Claude-Antigravity-Workspace](https://github.com/ibrahimalkateb965-tech/Claude-Antigravity-Workspace) على GitHub بنقرة واحدة.
 &lt;/div&gt;</t>
         </is>
       </c>
@@ -2513,7 +2514,7 @@
         <is>
           <t>* **طريقة العمل والإجراءات:**
   1. **فحص وتقييم المورد (`resource-scout-integrator` + `github-talent-scout`):** استلام رابط المستودع الخارجي وفحص ملفات README والأكواد وتحديد ما إذا كان يُحدث نقلة نوعية واستبعاد ما لا يتوافق مع البيئة.
-  2. **بناء وهيكلة المهارات (`skill-forge-builder`):** استخراج المهارات الفعالة وصياغة ملفات `SKILL.md` وفق المعايير العالمية.
+  2. **بناء وهيكلة المهارات (`skill-forge-builder`):** استخراج المهارات الفعالة وصياغة ملفات `SKILL.md` وفق المعايير العالمية عبر `skill-creator` و `find-skills`.
   3. **التعميم العالمي (`global-deployment`):** نشر المهارات في `C:\Users\Kt\.gemini\config\skills/` لتصبح متاحة لكل المشاريع.
   4. **تحديث الخطافات والإكسيل وتطبيق مكتبة الأوامر ودليل المستخدم (`agent-optimizer` + `frontend-design-builder`):** إضافة المهارات للخطافات ذات الصلة، وتحديث `hooks_user_guide.md` و `USER_GUIDE.md`، وتشغيل سكربت `convert_hooks_to_sheets.py` لتحديث ملف الإكسيل `HOOKS_GUIDE.xlsx` وتشغيل `update_html.py` لتحديث تطبيق مكتبة الأوامر التفاعلي (`03_Dynamic_Prompt_Library/index.html`).
   5. **مزامنة المستودع العام سحابياً (`git-github-manager`):** تشغيل `sync_global_ecosystem.py` لمزامنة كامل منظومة الوكلاء والمهارات والدليل مع مستودع `Claude-Antigravity-Workspace` ورفعه إلى GitHub.</t>
@@ -2586,12 +2587,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20. خطاف المزامنة السحابية الشاملة للمنظومة</t>
+          <t>20. خطاف المزامنة السحابية الشاملة ومطابقة المنظومة</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>مزامنة عالمية, مزامنة المنظومة, مزامنة المستودع, تحديث السحابة, sync ecosystem, global sync</t>
+          <t>مزامنة المنظومة, مزامنة المستودع العام, تحديث المنظومة العالمية, sync ecosystem, sync workspace</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2602,21 +2603,22 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[resource-scout-integrator], [git-github-manager], [agent-optimizer], [frontend-design-builder]</t>
+          <t>[git-github-manager], [persistent-memory-engine], [agent-optimizer], [docs-guard]</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>مزامنة 100% لكافة المكونات العالمية (المهارات، الوكلاء، الإضافات، المراجع، الإكسيل، وتطبيق HTML) ورفعها لمستودع Claude-Antigravity-Workspace على GitHub.</t>
+          <t>مطابقة ومزامنة كافة الإضافات (Plugins)، المراجع والذاكرة، إعدادات MCP، المهارات والوكلاء، وتحديث الإكسيل ومكتبة الأوامر، ورفعها لـ GitHub بتطابق 100%.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **تحديث مصنف الإكسيل وتطبيق الأوامر:** تشغيل `convert_hooks_to_sheets.py` لتحديث ملف الإكسيل التفاعلي `HOOKS_GUIDE.xlsx` وتشغيل `update_html.py` لتحديث تطبيق مكتبة الأوامر الذكية `index.html`.
-  2. **مزامنة المهارات والوكلاء والإضافات العالمية:** نسخ كافة المهارات (80+) والوكلاء (25+) والإضافات الـ 8 (`plugins/`) والمراجع وبذور المشاريع وإعدادات MCP من مسارات النظام العالمي (`~/.gemini/config/`) والمحلي إلى مستودع المنظومة.
-  3. **مطابقة وتحديث أدلة المستخدم:** تحديث `hooks_user_guide.md` و `USER_GUIDE.md` و `README.md` لتعكس كافة الإضافات والترقيات الحديثة.
-  4. **الالتزام والدفع السحابي إلى GitHub:** تنفيذ `git commit` موثق ودفع كافة الملفات والمجلدات إلى مستودع [Claude-Antigravity-Workspace](https://github.com/ibrahimalkateb965-tech/Claude-Antigravity-Workspace) على GitHub بنقرة واحدة وإصدار تقرير النجاح.
+  1. **التحقق من سلامة المكونات والبيئة (`agent-optimizer`):** فحص حزم الإضافات (Plugins)، المهارات، والوكلاء والتكوينات العالمية في `~/.gemini/config/` ومقارنتها بالمشروع.
+  2. **تحديث ملفات الإكسيل وتطبيق مكتبة الأوامر:** تشغيل `convert_hooks_to_sheets.py` و `update_html.py` لتحديث `HOOKS_GUIDE.xlsx` و `index.html` بكافة الخطافات وتفاصيلها.
+  3. **تشغيل محرك المزامنة الشاملة (`sync_global_ecosystem.py`):** نسخ ومطابقة كافة الإضافات (Plugins)، والمراجع والذاكرة (References)، والمهارات، والوكلاء، وإعدادات MCP إلى `Claude-Antigravity-Workspace` بضمان تطابق 100%.
+  4. **فحص ومطابقة التوثيق (`docs-guard`):** مراجعة سلامة `README.md`, `USER_GUIDE.md`, `hooks_user_guide.md` لضمان عدم وجود أي انحراف.
+  5. **الالتزام والرفع التلقائي إلى GitHub (`git-github-manager`):** تنفيذ `git commit` موثق ودفع كافة التحديثات إلى المستودع العام [Claude-Antigravity-Workspace](https://github.com/ibrahimalkateb965-tech/Claude-Antigravity-Workspace) على GitHub بنقرة واحدة.
 &lt;/div&gt;</t>
         </is>
       </c>
